--- a/Experiments/outputs/scenario_5.xlsx
+++ b/Experiments/outputs/scenario_5.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3840.828172892832</v>
+        <v>3817.274404759614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5817780494689941</v>
+        <v>1.147469997406006</v>
       </c>
       <c r="E2" t="n">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="H2" t="n">
-        <v>3262.433143143221</v>
+        <v>3243.577064810363</v>
       </c>
       <c r="I2" t="n">
-        <v>1.832585096359253</v>
+        <v>15.37012505531311</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="K2" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L2" t="n">
-        <v>523</v>
+        <v>629</v>
       </c>
       <c r="M2" t="n">
-        <v>4859.485270363518</v>
+        <v>4841.123376647568</v>
       </c>
       <c r="N2" t="n">
-        <v>4.48179817199707</v>
+        <v>4.545108795166016</v>
       </c>
       <c r="O2" t="n">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="P2" t="n">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="Q2" t="n">
-        <v>1717</v>
+        <v>1777</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2096224272317806</v>
+        <v>0.2114899564069693</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3286463562221742</v>
+        <v>0.3299949593400965</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3785.077714043675</v>
+        <v>4037.700599233087</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9455077648162842</v>
+        <v>1.170702934265137</v>
       </c>
       <c r="E3" t="n">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
-        <v>3316.202202072324</v>
+        <v>3214.794533551162</v>
       </c>
       <c r="I3" t="n">
-        <v>3.100320100784302</v>
+        <v>13.50711393356323</v>
       </c>
       <c r="J3" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K3" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
-        <v>528</v>
+        <v>618</v>
       </c>
       <c r="M3" t="n">
-        <v>4843.733926783557</v>
+        <v>4835.594175828886</v>
       </c>
       <c r="N3" t="n">
-        <v>5.902030944824219</v>
+        <v>4.188101291656494</v>
       </c>
       <c r="O3" t="n">
-        <v>574</v>
+        <v>641</v>
       </c>
       <c r="P3" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q3" t="n">
-        <v>1583</v>
+        <v>1748</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2185620078935414</v>
+        <v>0.1650042471686593</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3153624348077224</v>
+        <v>0.3351810725514196</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4208.944558098857</v>
+        <v>4040.987902475232</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4716522693634033</v>
+        <v>0.9412360191345215</v>
       </c>
       <c r="E4" t="n">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H4" t="n">
-        <v>3211.177520263368</v>
+        <v>3117.649948904476</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72848105430603</v>
+        <v>13.20125699043274</v>
       </c>
       <c r="J4" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
-        <v>494</v>
+        <v>592</v>
       </c>
       <c r="M4" t="n">
-        <v>4813.506059761087</v>
+        <v>4836.062142978089</v>
       </c>
       <c r="N4" t="n">
-        <v>5.32964825630188</v>
+        <v>4.332664251327515</v>
       </c>
       <c r="O4" t="n">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="P4" t="n">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="Q4" t="n">
-        <v>1686</v>
+        <v>1776</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1255969129687223</v>
+        <v>0.164405298566582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3328817954323399</v>
+        <v>0.3553329430575513</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3520.778325865491</v>
+        <v>3980.255624359572</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5467157363891602</v>
+        <v>1.103754997253418</v>
       </c>
       <c r="E5" t="n">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="H5" t="n">
-        <v>3247.227598644829</v>
+        <v>3409.488245718421</v>
       </c>
       <c r="I5" t="n">
-        <v>1.478049993515015</v>
+        <v>13.93877816200256</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L5" t="n">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="M5" t="n">
-        <v>4692.53437183142</v>
+        <v>4834.529499334968</v>
       </c>
       <c r="N5" t="n">
-        <v>5.227787971496582</v>
+        <v>4.542092084884644</v>
       </c>
       <c r="O5" t="n">
-        <v>594</v>
+        <v>541</v>
       </c>
       <c r="P5" t="n">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="Q5" t="n">
-        <v>1757</v>
+        <v>1634</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2497064385931415</v>
+        <v>0.1767025881407712</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3080013184053697</v>
+        <v>0.2947631726753501</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3967.923634883556</v>
+        <v>3688.565360551305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4537379741668701</v>
+        <v>0.8941781520843506</v>
       </c>
       <c r="E6" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H6" t="n">
-        <v>3275.815782716113</v>
+        <v>3350.2826501126</v>
       </c>
       <c r="I6" t="n">
-        <v>1.56383204460144</v>
+        <v>9.394024133682251</v>
       </c>
       <c r="J6" t="n">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L6" t="n">
-        <v>527</v>
+        <v>561</v>
       </c>
       <c r="M6" t="n">
-        <v>4823.350511617083</v>
+        <v>4783.088271075618</v>
       </c>
       <c r="N6" t="n">
-        <v>5.084003925323486</v>
+        <v>4.939146041870117</v>
       </c>
       <c r="O6" t="n">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="P6" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Q6" t="n">
-        <v>1560</v>
+        <v>1693</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1773511741834277</v>
+        <v>0.2288318443009158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.320842270362421</v>
+        <v>0.2995565918420338</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4052.784185092649</v>
+        <v>3903.994150671381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4886050224304199</v>
+        <v>1.438081741333008</v>
       </c>
       <c r="E7" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H7" t="n">
-        <v>3407.585791794679</v>
+        <v>3400.26261903851</v>
       </c>
       <c r="I7" t="n">
-        <v>1.817342281341553</v>
+        <v>12.85286402702332</v>
       </c>
       <c r="J7" t="n">
         <v>422</v>
       </c>
       <c r="K7" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L7" t="n">
-        <v>498</v>
+        <v>597</v>
       </c>
       <c r="M7" t="n">
-        <v>4812.106048418465</v>
+        <v>4745.82219309456</v>
       </c>
       <c r="N7" t="n">
-        <v>4.642412662506104</v>
+        <v>5.002253770828247</v>
       </c>
       <c r="O7" t="n">
-        <v>618</v>
+        <v>577</v>
       </c>
       <c r="P7" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q7" t="n">
-        <v>1768</v>
+        <v>1626</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1577940834399053</v>
+        <v>0.1773829714160144</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2918722576958571</v>
+        <v>0.2835250709590248</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4076.380643580823</v>
+        <v>3301.9685360902</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9103941917419434</v>
+        <v>1.145123958587646</v>
       </c>
       <c r="E8" t="n">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H8" t="n">
-        <v>3240.040492966376</v>
+        <v>3239.464628059262</v>
       </c>
       <c r="I8" t="n">
-        <v>1.927402019500732</v>
+        <v>12.88160610198975</v>
       </c>
       <c r="J8" t="n">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L8" t="n">
-        <v>518</v>
+        <v>602</v>
       </c>
       <c r="M8" t="n">
-        <v>4846.477525456277</v>
+        <v>4755.22264186269</v>
       </c>
       <c r="N8" t="n">
-        <v>4.269349098205566</v>
+        <v>4.566972017288208</v>
       </c>
       <c r="O8" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="P8" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="Q8" t="n">
-        <v>1618</v>
+        <v>1850</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1588982674180363</v>
+        <v>0.3056122110831868</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3314648678451597</v>
+        <v>0.318756476397009</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4135.132868602064</v>
+        <v>3864.068669856369</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4878461360931396</v>
+        <v>1.281387090682983</v>
       </c>
       <c r="E9" t="n">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="H9" t="n">
-        <v>3271.56406281202</v>
+        <v>3364.765914488722</v>
       </c>
       <c r="I9" t="n">
-        <v>1.461839914321899</v>
+        <v>14.19928312301636</v>
       </c>
       <c r="J9" t="n">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L9" t="n">
-        <v>514</v>
+        <v>646</v>
       </c>
       <c r="M9" t="n">
-        <v>4961.807518524444</v>
+        <v>4811.335858673177</v>
       </c>
       <c r="N9" t="n">
-        <v>4.834166049957275</v>
+        <v>4.491037368774414</v>
       </c>
       <c r="O9" t="n">
-        <v>530</v>
+        <v>602</v>
       </c>
       <c r="P9" t="n">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="Q9" t="n">
-        <v>1511</v>
+        <v>1842</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1666075612236201</v>
+        <v>0.1968823662786319</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3406507506391689</v>
+        <v>0.3006586916140533</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3928.490387400166</v>
+        <v>3648.620442292002</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4848160743713379</v>
+        <v>1.413177013397217</v>
       </c>
       <c r="E10" t="n">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H10" t="n">
-        <v>3314.440466484241</v>
+        <v>3252.576415359283</v>
       </c>
       <c r="I10" t="n">
-        <v>1.432050943374634</v>
+        <v>14.00988483428955</v>
       </c>
       <c r="J10" t="n">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="K10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>501</v>
+        <v>616</v>
       </c>
       <c r="M10" t="n">
-        <v>4815.378489272927</v>
+        <v>4639.187525938422</v>
       </c>
       <c r="N10" t="n">
-        <v>5.032449960708618</v>
+        <v>4.307629823684692</v>
       </c>
       <c r="O10" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="P10" t="n">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="Q10" t="n">
-        <v>1705</v>
+        <v>1620</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1841782746358266</v>
+        <v>0.213521673376643</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3116967910481554</v>
+        <v>0.298890937869267</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4099.50522625026</v>
+        <v>3576.221314352455</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5612916946411133</v>
+        <v>1.457904815673828</v>
       </c>
       <c r="E11" t="n">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H11" t="n">
-        <v>3640.540441645453</v>
+        <v>3245.270067554646</v>
       </c>
       <c r="I11" t="n">
-        <v>1.797109842300415</v>
+        <v>11.95040106773376</v>
       </c>
       <c r="J11" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K11" t="n">
         <v>74</v>
       </c>
       <c r="L11" t="n">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="M11" t="n">
-        <v>4864.514756674056</v>
+        <v>4858.067245598759</v>
       </c>
       <c r="N11" t="n">
-        <v>4.215819835662842</v>
+        <v>4.147420167922974</v>
       </c>
       <c r="O11" t="n">
-        <v>612</v>
+        <v>570</v>
       </c>
       <c r="P11" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="Q11" t="n">
-        <v>1700</v>
+        <v>1662</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1572632767480482</v>
+        <v>0.2638592399904741</v>
       </c>
       <c r="S11" t="n">
-        <v>0.251612828052238</v>
+        <v>0.3319832963418222</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4032.80578309417</v>
+        <v>3817.760551811844</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4849419593811035</v>
+        <v>1.372923135757446</v>
       </c>
       <c r="E12" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H12" t="n">
-        <v>3119.42782456397</v>
+        <v>3447.985128863666</v>
       </c>
       <c r="I12" t="n">
-        <v>1.559823274612427</v>
+        <v>13.74309301376343</v>
       </c>
       <c r="J12" t="n">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="L12" t="n">
-        <v>520</v>
+        <v>590</v>
       </c>
       <c r="M12" t="n">
-        <v>4836.215920548727</v>
+        <v>4892.726337267968</v>
       </c>
       <c r="N12" t="n">
-        <v>4.822623014450073</v>
+        <v>4.403162240982056</v>
       </c>
       <c r="O12" t="n">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="P12" t="n">
         <v>411</v>
       </c>
       <c r="Q12" t="n">
-        <v>1694</v>
+        <v>1730</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1661237113175461</v>
+        <v>0.2197069100857111</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3549858244935363</v>
+        <v>0.2952834695453305</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4501.379905509203</v>
+        <v>3771.76748158846</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4676361083984375</v>
+        <v>1.09738302230835</v>
       </c>
       <c r="E13" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H13" t="n">
-        <v>3672.932448652238</v>
+        <v>3388.978999098435</v>
       </c>
       <c r="I13" t="n">
-        <v>1.495429039001465</v>
+        <v>12.22754693031311</v>
       </c>
       <c r="J13" t="n">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="K13" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="L13" t="n">
-        <v>476</v>
+        <v>598</v>
       </c>
       <c r="M13" t="n">
-        <v>4799.751114098769</v>
+        <v>4690.602314770258</v>
       </c>
       <c r="N13" t="n">
-        <v>5.195520162582397</v>
+        <v>4.794343948364258</v>
       </c>
       <c r="O13" t="n">
-        <v>506</v>
+        <v>600</v>
       </c>
       <c r="P13" t="n">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="Q13" t="n">
-        <v>1336</v>
+        <v>1700</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0621638917303715</v>
+        <v>0.195888453448393</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2347660615436119</v>
+        <v>0.277495986298633</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3910.354068861805</v>
+        <v>3766.385500249155</v>
       </c>
       <c r="D14" t="n">
-        <v>0.519585132598877</v>
+        <v>0.9533240795135498</v>
       </c>
       <c r="E14" t="n">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H14" t="n">
-        <v>3433.737683941361</v>
+        <v>3178.10719782655</v>
       </c>
       <c r="I14" t="n">
-        <v>1.537555932998657</v>
+        <v>13.60225510597229</v>
       </c>
       <c r="J14" t="n">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="K14" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L14" t="n">
-        <v>512</v>
+        <v>594</v>
       </c>
       <c r="M14" t="n">
-        <v>4850.352079540066</v>
+        <v>4944.52252510591</v>
       </c>
       <c r="N14" t="n">
-        <v>4.243215084075928</v>
+        <v>4.884752035140991</v>
       </c>
       <c r="O14" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="P14" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="Q14" t="n">
-        <v>1411</v>
+        <v>1646</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1937999541607289</v>
+        <v>0.2382711412223813</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2920642403619153</v>
+        <v>0.3572468966033326</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3556.848978432392</v>
+        <v>3972.786267086227</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6274700164794922</v>
+        <v>1.152752161026001</v>
       </c>
       <c r="E15" t="n">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="H15" t="n">
-        <v>3167.271855623957</v>
+        <v>3142.498654509359</v>
       </c>
       <c r="I15" t="n">
-        <v>1.858200073242188</v>
+        <v>12.6254620552063</v>
       </c>
       <c r="J15" t="n">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="K15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>501</v>
+        <v>616</v>
       </c>
       <c r="M15" t="n">
-        <v>4692.833410555912</v>
+        <v>4799.776767813225</v>
       </c>
       <c r="N15" t="n">
-        <v>4.557937145233154</v>
+        <v>4.961941003799438</v>
       </c>
       <c r="O15" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="P15" t="n">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="Q15" t="n">
-        <v>1684</v>
+        <v>1669</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2420679220294229</v>
+        <v>0.1722977006498937</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3250832538611758</v>
+        <v>0.3452823315487067</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4120.609006707201</v>
+        <v>3863.967936003723</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4580888748168945</v>
+        <v>0.9007439613342285</v>
       </c>
       <c r="E16" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H16" t="n">
-        <v>3060.55513049107</v>
+        <v>3432.31475279148</v>
       </c>
       <c r="I16" t="n">
-        <v>1.398809909820557</v>
+        <v>12.73979330062866</v>
       </c>
       <c r="J16" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="L16" t="n">
-        <v>494</v>
+        <v>619</v>
       </c>
       <c r="M16" t="n">
-        <v>4808.050102489991</v>
+        <v>4802.976536992874</v>
       </c>
       <c r="N16" t="n">
-        <v>5.076700925827026</v>
+        <v>4.864486932754517</v>
       </c>
       <c r="O16" t="n">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="P16" t="n">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="Q16" t="n">
-        <v>1737</v>
+        <v>1749</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1429771073780572</v>
+        <v>0.1955055565557812</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3634519056059606</v>
+        <v>0.2853775723542386</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3638.07155060216</v>
+        <v>3818.978506875006</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6058831214904785</v>
+        <v>1.144252777099609</v>
       </c>
       <c r="E17" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H17" t="n">
-        <v>3386.325443360821</v>
+        <v>3665.82607558854</v>
       </c>
       <c r="I17" t="n">
-        <v>1.600257158279419</v>
+        <v>13.5658130645752</v>
       </c>
       <c r="J17" t="n">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L17" t="n">
-        <v>513</v>
+        <v>580</v>
       </c>
       <c r="M17" t="n">
-        <v>4620.57480270677</v>
+        <v>4865.344453909052</v>
       </c>
       <c r="N17" t="n">
-        <v>5.059900045394897</v>
+        <v>4.748336791992188</v>
       </c>
       <c r="O17" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P17" t="n">
-        <v>373</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="n">
-        <v>1638</v>
+        <v>1649</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2126365861513706</v>
+        <v>0.2150651319647771</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2671203068983789</v>
+        <v>0.2465433618696332</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4038.204672845467</v>
+        <v>4385.152613072045</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4260971546173096</v>
+        <v>1.243550300598145</v>
       </c>
       <c r="E18" t="n">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="F18" t="n">
         <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="H18" t="n">
-        <v>3299.958877308819</v>
+        <v>3248.890960685352</v>
       </c>
       <c r="I18" t="n">
-        <v>1.834536790847778</v>
+        <v>11.80345702171326</v>
       </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="K18" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L18" t="n">
-        <v>522</v>
+        <v>595</v>
       </c>
       <c r="M18" t="n">
-        <v>4720.720320725616</v>
+        <v>5005.706664133917</v>
       </c>
       <c r="N18" t="n">
-        <v>4.780441045761108</v>
+        <v>4.481630086898804</v>
       </c>
       <c r="O18" t="n">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="P18" t="n">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="Q18" t="n">
-        <v>1816</v>
+        <v>1755</v>
       </c>
       <c r="R18" t="n">
-        <v>0.144578708652505</v>
+        <v>0.1239693199579923</v>
       </c>
       <c r="S18" t="n">
-        <v>0.300962850347045</v>
+        <v>0.3509625755812297</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3678.774655115096</v>
+        <v>3598.5703021083</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5672707557678223</v>
+        <v>1.168510913848877</v>
       </c>
       <c r="E19" t="n">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H19" t="n">
-        <v>3111.313933461657</v>
+        <v>3086.506767553031</v>
       </c>
       <c r="I19" t="n">
-        <v>1.903578996658325</v>
+        <v>11.43315196037292</v>
       </c>
       <c r="J19" t="n">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="K19" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L19" t="n">
-        <v>518</v>
+        <v>586</v>
       </c>
       <c r="M19" t="n">
-        <v>4902.691580679272</v>
+        <v>4838.866282206657</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6922607421875</v>
+        <v>4.477662086486816</v>
       </c>
       <c r="O19" t="n">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="P19" t="n">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="Q19" t="n">
-        <v>1682</v>
+        <v>1615</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2496418355964788</v>
+        <v>0.2563195401078015</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3653865673046107</v>
+        <v>0.3621425789543624</v>
       </c>
     </row>
     <row r="20">
@@ -1628,25 +1628,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3634.566615314171</v>
+        <v>3727.930081987456</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6042139530181885</v>
+        <v>1.13520622253418</v>
       </c>
       <c r="E20" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H20" t="n">
-        <v>3242.323769529966</v>
+        <v>3389.791645151807</v>
       </c>
       <c r="I20" t="n">
-        <v>1.652249097824097</v>
+        <v>13.62340712547302</v>
       </c>
       <c r="J20" t="n">
         <v>458</v>
@@ -1655,28 +1655,28 @@
         <v>66</v>
       </c>
       <c r="L20" t="n">
-        <v>523</v>
+        <v>627</v>
       </c>
       <c r="M20" t="n">
-        <v>4850.354166869293</v>
+        <v>4791.413088947481</v>
       </c>
       <c r="N20" t="n">
-        <v>5.06880521774292</v>
+        <v>4.719074010848999</v>
       </c>
       <c r="O20" t="n">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="P20" t="n">
         <v>420</v>
       </c>
       <c r="Q20" t="n">
-        <v>1624</v>
+        <v>1781</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2506595414948563</v>
+        <v>0.2219560257522355</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3315284496796336</v>
+        <v>0.2925277820501103</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3837.708635389004</v>
+        <v>4075.27646776469</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4989039897918701</v>
+        <v>1.131978988647461</v>
       </c>
       <c r="E21" t="n">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H21" t="n">
-        <v>3367.767786474179</v>
+        <v>3142.314775951212</v>
       </c>
       <c r="I21" t="n">
-        <v>1.570397138595581</v>
+        <v>11.93465113639832</v>
       </c>
       <c r="J21" t="n">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="K21" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L21" t="n">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="M21" t="n">
-        <v>4888.258874573125</v>
+        <v>4889.852079205985</v>
       </c>
       <c r="N21" t="n">
-        <v>4.910706043243408</v>
+        <v>4.737826108932495</v>
       </c>
       <c r="O21" t="n">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="P21" t="n">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="Q21" t="n">
-        <v>1506</v>
+        <v>1607</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2149129712930481</v>
+        <v>0.1665849187760229</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3110496246440561</v>
+        <v>0.3573804023001323</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4036.678405685766</v>
+        <v>4017.344997237755</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6711688041687012</v>
+        <v>0.9779829978942871</v>
       </c>
       <c r="E22" t="n">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F22" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="H22" t="n">
-        <v>3180.151399815804</v>
+        <v>3028.243158973072</v>
       </c>
       <c r="I22" t="n">
-        <v>1.611000776290894</v>
+        <v>12.23700976371765</v>
       </c>
       <c r="J22" t="n">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="K22" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="L22" t="n">
-        <v>492</v>
+        <v>605</v>
       </c>
       <c r="M22" t="n">
-        <v>4751.585278563704</v>
+        <v>4800.68284838609</v>
       </c>
       <c r="N22" t="n">
-        <v>4.57704496383667</v>
+        <v>4.874616146087646</v>
       </c>
       <c r="O22" t="n">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="P22" t="n">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="Q22" t="n">
-        <v>1744</v>
+        <v>1595</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1504564962988602</v>
+        <v>0.1631721727694801</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3307178102931804</v>
+        <v>0.3692057453886759</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3939.772164100395</v>
+        <v>4047.744006088591</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6197390556335449</v>
+        <v>1.112707138061523</v>
       </c>
       <c r="E23" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G23" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H23" t="n">
-        <v>3340.923676405695</v>
+        <v>3244.172469940483</v>
       </c>
       <c r="I23" t="n">
-        <v>1.773704767227173</v>
+        <v>16.69822883605957</v>
       </c>
       <c r="J23" t="n">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="M23" t="n">
-        <v>4783.074315565412</v>
+        <v>4811.784379939952</v>
       </c>
       <c r="N23" t="n">
-        <v>4.57111382484436</v>
+        <v>5.348599195480347</v>
       </c>
       <c r="O23" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P23" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="Q23" t="n">
-        <v>1678</v>
+        <v>1742</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1763096485289146</v>
+        <v>0.1587852475344907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3015112339916128</v>
+        <v>0.3257859842046854</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4100.637720509381</v>
+        <v>4059.20529189475</v>
       </c>
       <c r="D24" t="n">
-        <v>0.469365119934082</v>
+        <v>1.156730890274048</v>
       </c>
       <c r="E24" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H24" t="n">
-        <v>3176.748010898749</v>
+        <v>3348.66437045631</v>
       </c>
       <c r="I24" t="n">
-        <v>1.713112115859985</v>
+        <v>12.5977737903595</v>
       </c>
       <c r="J24" t="n">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="K24" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="L24" t="n">
-        <v>529</v>
+        <v>606</v>
       </c>
       <c r="M24" t="n">
-        <v>4894.733101793953</v>
+        <v>4941.182199658146</v>
       </c>
       <c r="N24" t="n">
-        <v>5.471950054168701</v>
+        <v>4.490430116653442</v>
       </c>
       <c r="O24" t="n">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="P24" t="n">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="Q24" t="n">
-        <v>1498</v>
+        <v>1844</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1622346642339969</v>
+        <v>0.1784951196141715</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3509864695718651</v>
+        <v>0.3222949012712005</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3964.689722728156</v>
+        <v>4114.936695663696</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4680171012878418</v>
+        <v>0.9938161373138428</v>
       </c>
       <c r="E25" t="n">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G25" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="H25" t="n">
-        <v>3117.809201076735</v>
+        <v>3413.013156217789</v>
       </c>
       <c r="I25" t="n">
-        <v>1.499310255050659</v>
+        <v>13.90268182754517</v>
       </c>
       <c r="J25" t="n">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L25" t="n">
-        <v>505</v>
+        <v>589</v>
       </c>
       <c r="M25" t="n">
-        <v>4857.03708554856</v>
+        <v>4974.199451948843</v>
       </c>
       <c r="N25" t="n">
-        <v>4.996685743331909</v>
+        <v>4.317298889160156</v>
       </c>
       <c r="O25" t="n">
-        <v>602</v>
+        <v>511</v>
       </c>
       <c r="P25" t="n">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="Q25" t="n">
-        <v>1731</v>
+        <v>1461</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1837225755338495</v>
+        <v>0.172743928864472</v>
       </c>
       <c r="S25" t="n">
-        <v>0.358084126976641</v>
+        <v>0.3138567946083055</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3764.303308992938</v>
+        <v>3820.000613898779</v>
       </c>
       <c r="D26" t="n">
-        <v>0.632896900177002</v>
+        <v>1.155400991439819</v>
       </c>
       <c r="E26" t="n">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F26" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H26" t="n">
-        <v>3602.12424186467</v>
+        <v>3296.952633465497</v>
       </c>
       <c r="I26" t="n">
-        <v>1.804434776306152</v>
+        <v>13.43061900138855</v>
       </c>
       <c r="J26" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L26" t="n">
-        <v>493</v>
+        <v>595</v>
       </c>
       <c r="M26" t="n">
-        <v>4883.01471508564</v>
+        <v>4888.984838111782</v>
       </c>
       <c r="N26" t="n">
-        <v>5.318991899490356</v>
+        <v>4.589347124099731</v>
       </c>
       <c r="O26" t="n">
-        <v>608</v>
+        <v>573</v>
       </c>
       <c r="P26" t="n">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="Q26" t="n">
-        <v>1935</v>
+        <v>1707</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2291026079926695</v>
+        <v>0.2186515727927404</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2623155054732424</v>
+        <v>0.3256365600146058</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3947.94846979387</v>
+        <v>3930.015127324677</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6920292377471924</v>
+        <v>1.031809091567993</v>
       </c>
       <c r="E27" t="n">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="F27" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G27" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H27" t="n">
-        <v>3182.832219119291</v>
+        <v>3332.676043827604</v>
       </c>
       <c r="I27" t="n">
-        <v>1.802009105682373</v>
+        <v>13.17319416999817</v>
       </c>
       <c r="J27" t="n">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="K27" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L27" t="n">
-        <v>507</v>
+        <v>616</v>
       </c>
       <c r="M27" t="n">
-        <v>4780.822906088857</v>
+        <v>4879.120709737859</v>
       </c>
       <c r="N27" t="n">
-        <v>5.151561975479126</v>
+        <v>4.51674222946167</v>
       </c>
       <c r="O27" t="n">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="P27" t="n">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="Q27" t="n">
-        <v>1709</v>
+        <v>1605</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1742115222955107</v>
+        <v>0.1945238986440601</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3342501319039374</v>
+        <v>0.3169515078452201</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3981.422353311987</v>
+        <v>4027.578149054326</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6053388118743896</v>
+        <v>1.077116012573242</v>
       </c>
       <c r="E28" t="n">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H28" t="n">
-        <v>3160.170872514156</v>
+        <v>3387.232359776188</v>
       </c>
       <c r="I28" t="n">
-        <v>1.866983890533447</v>
+        <v>15.31807899475098</v>
       </c>
       <c r="J28" t="n">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="K28" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L28" t="n">
-        <v>486</v>
+        <v>618</v>
       </c>
       <c r="M28" t="n">
-        <v>4722.4718709975</v>
+        <v>4921.071146106703</v>
       </c>
       <c r="N28" t="n">
-        <v>4.675321102142334</v>
+        <v>4.384005784988403</v>
       </c>
       <c r="O28" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="P28" t="n">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="Q28" t="n">
-        <v>1524</v>
+        <v>1556</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1569198373073604</v>
+        <v>0.1815647387579963</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3308227219050325</v>
+        <v>0.31168799246969</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4194.879967912224</v>
+        <v>4147.138289583692</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4508659839630127</v>
+        <v>0.7500021457672119</v>
       </c>
       <c r="E29" t="n">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G29" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>3257.45777444066</v>
+        <v>3466.982637590032</v>
       </c>
       <c r="I29" t="n">
-        <v>1.54081392288208</v>
+        <v>12.57694625854492</v>
       </c>
       <c r="J29" t="n">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="K29" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="L29" t="n">
-        <v>526</v>
+        <v>596</v>
       </c>
       <c r="M29" t="n">
-        <v>4807.26013521369</v>
+        <v>4861.781936539933</v>
       </c>
       <c r="N29" t="n">
-        <v>5.023419141769409</v>
+        <v>4.887824296951294</v>
       </c>
       <c r="O29" t="n">
-        <v>576</v>
+        <v>541</v>
       </c>
       <c r="P29" t="n">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="Q29" t="n">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1273865258124303</v>
+        <v>0.1469921226999422</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3223878710911781</v>
+        <v>0.2868905510687223</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4087.552617435281</v>
+        <v>4060.282410426419</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4892630577087402</v>
+        <v>0.9548649787902832</v>
       </c>
       <c r="E30" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F30" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G30" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H30" t="n">
-        <v>3386.016924943532</v>
+        <v>3304.905587833498</v>
       </c>
       <c r="I30" t="n">
-        <v>1.500066041946411</v>
+        <v>14.35964012145996</v>
       </c>
       <c r="J30" t="n">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="K30" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L30" t="n">
-        <v>490</v>
+        <v>615</v>
       </c>
       <c r="M30" t="n">
-        <v>4759.072066520765</v>
+        <v>4805.880450113158</v>
       </c>
       <c r="N30" t="n">
-        <v>5.326189041137695</v>
+        <v>4.878565073013306</v>
       </c>
       <c r="O30" t="n">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="P30" t="n">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="Q30" t="n">
-        <v>1892</v>
+        <v>1756</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1411030217023829</v>
+        <v>0.1551428603824682</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2885132064371191</v>
+        <v>0.3123204744396666</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3901.516485424921</v>
+        <v>3513.060410097406</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6447732448577881</v>
+        <v>0.9767279624938965</v>
       </c>
       <c r="E31" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H31" t="n">
-        <v>3276.775265141183</v>
+        <v>3020.301861421829</v>
       </c>
       <c r="I31" t="n">
-        <v>1.557029008865356</v>
+        <v>12.13265991210938</v>
       </c>
       <c r="J31" t="n">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="K31" t="n">
         <v>62</v>
       </c>
       <c r="L31" t="n">
-        <v>510</v>
+        <v>592</v>
       </c>
       <c r="M31" t="n">
-        <v>4805.274236316531</v>
+        <v>4733.295807618519</v>
       </c>
       <c r="N31" t="n">
-        <v>5.863839149475098</v>
+        <v>4.736253976821899</v>
       </c>
       <c r="O31" t="n">
-        <v>540</v>
+        <v>589</v>
       </c>
       <c r="P31" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="Q31" t="n">
-        <v>1458</v>
+        <v>1711</v>
       </c>
       <c r="R31" t="n">
-        <v>0.188076206777406</v>
+        <v>0.2577982545601886</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3180877710627841</v>
+        <v>0.3619029986335367</v>
       </c>
     </row>
   </sheetData>
